--- a/ExcelProject/RegisterCourse.xlsx
+++ b/ExcelProject/RegisterCourse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="47">
   <si>
     <t>Execute</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>MJU6504106415</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>ไม่พบการแจ้งเตือน</t>
@@ -167,7 +164,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -184,12 +181,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -254,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -274,17 +265,11 @@
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="3" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -597,14 +582,14 @@
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="11" width="7.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="8.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="15.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="33.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="55.005" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="12" width="27.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="12" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="9" width="7.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="10" width="8.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="10" width="15.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="10" width="33.71928571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="10" width="31.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="10" width="33.005" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="10" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21.75">
@@ -633,7 +618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="39">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="48">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -659,7 +644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="21.75">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -670,297 +655,295 @@
         <v>15</v>
       </c>
       <c r="D3" s="8"/>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="48.75">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="39">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="48.75">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="39">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="48.75">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="39">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="48.75">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="39">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="48.75">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="39">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="48.75">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="39">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="48.75">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="39">
-      <c r="A10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="48.75">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="39">
-      <c r="A11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="D11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="48.75">
+      <c r="A12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="39">
-      <c r="A12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="48.75">
+      <c r="A13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="39">
-      <c r="A13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="48.75">
+      <c r="A14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="39">
-      <c r="A14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>41</v>
-      </c>
       <c r="D14" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>21</v>
+      <c r="F14" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>13</v>
@@ -974,19 +957,19 @@
         <v>8</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>43</v>
-      </c>
       <c r="D15" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="10" t="s">
-        <v>21</v>
+      <c r="F15" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>13</v>
@@ -1000,19 +983,19 @@
         <v>8</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="D16" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="10" t="s">
-        <v>21</v>
+      <c r="F16" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>13</v>
@@ -1026,19 +1009,19 @@
         <v>8</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="D17" s="6" t="s">
         <v>11</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="10" t="s">
-        <v>21</v>
+      <c r="F17" s="7" t="s">
+        <v>20</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>13</v>
